--- a/example/reference_results/9_phyloseq_object/GTDB/phyloseq_summary_gtdb.xlsx
+++ b/example/reference_results/9_phyloseq_object/GTDB/phyloseq_summary_gtdb.xlsx
@@ -888,25 +888,25 @@
     <t xml:space="preserve">GTDB_raw_counts</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/5_dada2_pipeline/asv_count_table.csv</t>
+    <t xml:space="preserve">example/run_results/5_dada2_pipeline/asv_count_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">05131e8b84ef4c67e1b48fa1e18190c4</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/5_dada2_pipeline/gtdb_taxonomy_table.csv</t>
+    <t xml:space="preserve">example/run_results/5_dada2_pipeline/gtdb_taxonomy_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">caea23f786cb59c30c59f86f8d92d45f</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/data/metadata.tsv</t>
+    <t xml:space="preserve">example/data/metadata.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">9b55da3f786184f4f3e14c5e2d66458a</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/6_phylogenetic_tree/phylogenetic_tree.nwk</t>
+    <t xml:space="preserve">example/run_results/6_phylogenetic_tree/phylogenetic_tree.nwk</t>
   </si>
   <si>
     <t xml:space="preserve">9fd7281e253a6037e17c51803eee7fc7</t>
@@ -921,13 +921,13 @@
     <t xml:space="preserve">GTDB_copy_number_corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
+    <t xml:space="preserve">example/run_results/7_copy_number_correction/copy_number_corrected_asv_count_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">3b890108568d42995e867a47568550b0</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/7_copy_number_correction/copy_number_correction_summary.xlsx</t>
+    <t xml:space="preserve">example/run_results/7_copy_number_correction/copy_number_correction_summary.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">44ddd7389de9229f9cbce00fb188e4ae</t>
@@ -936,16 +936,16 @@
     <t xml:space="preserve">GTDB_microbial_load_corrected</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/8_microbial_load_correction/microbial_load_corrected_abundance_table.csv</t>
+    <t xml:space="preserve">example/run_results/8_microbial_load_correction/microbial_load_corrected_abundance_table.csv</t>
   </si>
   <si>
     <t xml:space="preserve">8d45406741bdc29c7d348c1fde74caa1</t>
   </si>
   <si>
-    <t xml:space="preserve">/Users/amro/Documents/workflows/DADA2_16S_PacBio_HiFi_Workflow/example/run_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">590f23d89dc8f85bc816ce3794ed192f</t>
+    <t xml:space="preserve">example/run_results/8_microbial_load_correction/microbial_load_correction_summary.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">658025efb8731f22cbd8d64f71cc5f99</t>
   </si>
   <si>
     <t xml:space="preserve">Sheet</t>
